--- a/sources_files/tests/COG-25-10 (predicted).xlsx
+++ b/sources_files/tests/COG-25-10 (predicted).xlsx
@@ -427,50 +427,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Hole ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>img_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>core_run_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>from</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>From (m)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>run_length</t>
+          <t>To (m)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>rqd_length</t>
+          <t>Run (m)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RQD (m)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>RQD (%)</t>
         </is>
@@ -479,2403 +485,2848 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_0</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="2" t="n">
-        <v>1.221711</v>
+        <v>57.549999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.221711</v>
+        <v>58.771709</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1.221711</v>
       </c>
       <c r="G2" s="2" t="n">
+        <v>1.221711</v>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_1</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>1.221711</v>
-      </c>
       <c r="D3" s="2" t="n">
-        <v>2.077325</v>
+        <v>58.771709</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.855615</v>
+        <v>59.627323</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.855615</v>
       </c>
       <c r="G3" s="2" t="n">
+        <v>0.855615</v>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_2</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>2.077325</v>
-      </c>
       <c r="D4" s="2" t="n">
-        <v>2.416561</v>
+        <v>59.627323</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.339236</v>
+        <v>59.96656</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.339236</v>
       </c>
       <c r="G4" s="2" t="n">
+        <v>0.339236</v>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_3</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>2.416561</v>
-      </c>
       <c r="D5" s="2" t="n">
-        <v>3.619333</v>
+        <v>59.96656</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.202772</v>
+        <v>61.169331</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1.202772</v>
       </c>
       <c r="G5" s="2" t="n">
+        <v>1.202772</v>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_4</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>3.619333</v>
-      </c>
       <c r="D6" s="2" t="n">
-        <v>4.771769</v>
+        <v>61.169331</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.152437</v>
+        <v>62.32177</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1.152437</v>
       </c>
       <c r="G6" s="2" t="n">
+        <v>1.152437</v>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_5</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>4.771769</v>
-      </c>
       <c r="D7" s="2" t="n">
-        <v>4.940296</v>
+        <v>62.32177</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.168527</v>
+        <v>62.490295</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.168527</v>
       </c>
       <c r="G7" s="2" t="n">
+        <v>0.168527</v>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_6</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>4.940296</v>
-      </c>
       <c r="D8" s="2" t="n">
-        <v>6.26013</v>
+        <v>62.490295</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.319835</v>
+        <v>63.810131</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1.319835</v>
       </c>
       <c r="G8" s="2" t="n">
+        <v>1.319835</v>
+      </c>
+      <c r="H8" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>6.26013</v>
-      </c>
       <c r="D9" s="2" t="n">
-        <v>7.546348</v>
+        <v>63.810131</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.286217</v>
+        <v>65.096344</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1.286217</v>
       </c>
       <c r="G9" s="2" t="n">
+        <v>1.286217</v>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_8</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>7.546348</v>
-      </c>
       <c r="D10" s="2" t="n">
-        <v>8.730433</v>
+        <v>65.096344</v>
       </c>
       <c r="E10" s="2" t="n">
+        <v>66.280434</v>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>1.184085</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>0.960315</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>81.10189099999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_9</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>8.730433</v>
-      </c>
       <c r="D11" s="2" t="n">
-        <v>10.028829</v>
+        <v>66.280434</v>
       </c>
       <c r="E11" s="2" t="n">
+        <v>67.578827</v>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>1.298396</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>1.10553</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>85.145798</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_10</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>10.028829</v>
-      </c>
       <c r="D12" s="2" t="n">
-        <v>10.289104</v>
+        <v>67.578827</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.260276</v>
+        <v>67.83910400000001</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0.260276</v>
       </c>
       <c r="G12" s="2" t="n">
+        <v>0.260276</v>
+      </c>
+      <c r="H12" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_11</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>10.289104</v>
-      </c>
       <c r="D13" s="2" t="n">
-        <v>11.276735</v>
+        <v>67.83910400000001</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.98763</v>
+        <v>68.826736</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0.98763</v>
       </c>
       <c r="G13" s="2" t="n">
+        <v>0.98763</v>
+      </c>
+      <c r="H13" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_12</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>11.276735</v>
-      </c>
       <c r="D14" s="2" t="n">
-        <v>12.577583</v>
+        <v>68.826736</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.300849</v>
+        <v>70.127579</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1.300849</v>
       </c>
       <c r="G14" s="2" t="n">
+        <v>1.300849</v>
+      </c>
+      <c r="H14" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_13</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="D15" s="2" t="n">
-        <v>0.5753549999999999</v>
+        <v>70.127579</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.5753549999999999</v>
+        <v>70.702934</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0.5753549999999999</v>
       </c>
       <c r="G15" s="2" t="n">
+        <v>0.5753549999999999</v>
+      </c>
+      <c r="H15" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_14</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>0.5753549999999999</v>
-      </c>
       <c r="D16" s="2" t="n">
-        <v>1.427193</v>
+        <v>70.702934</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.851838</v>
+        <v>71.554771</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0.851838</v>
       </c>
       <c r="G16" s="2" t="n">
+        <v>0.851838</v>
+      </c>
+      <c r="H16" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_15</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>1.427193</v>
-      </c>
       <c r="D17" s="2" t="n">
-        <v>2.710898</v>
+        <v>71.554771</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.283705</v>
+        <v>72.83847799999999</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1.283705</v>
       </c>
       <c r="G17" s="2" t="n">
+        <v>1.283705</v>
+      </c>
+      <c r="H17" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_16</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>2.710898</v>
-      </c>
       <c r="D18" s="2" t="n">
-        <v>3.584569</v>
+        <v>72.83847799999999</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.873671</v>
+        <v>73.71215100000001</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0.873671</v>
       </c>
       <c r="G18" s="2" t="n">
+        <v>0.873671</v>
+      </c>
+      <c r="H18" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_17</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>3.584569</v>
-      </c>
       <c r="D19" s="2" t="n">
-        <v>3.950656</v>
+        <v>73.71215100000001</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.366087</v>
+        <v>74.078232</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0.366087</v>
       </c>
       <c r="G19" s="2" t="n">
+        <v>0.366087</v>
+      </c>
+      <c r="H19" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_18</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>3.950656</v>
-      </c>
       <c r="D20" s="2" t="n">
-        <v>5.351896</v>
+        <v>74.078232</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.40124</v>
+        <v>75.479477</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1.40124</v>
       </c>
       <c r="G20" s="2" t="n">
+        <v>1.40124</v>
+      </c>
+      <c r="H20" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_19</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>5.351896</v>
-      </c>
       <c r="D21" s="2" t="n">
-        <v>6.363285</v>
+        <v>75.479477</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.011389</v>
+        <v>76.49086</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1.011389</v>
       </c>
       <c r="G21" s="2" t="n">
+        <v>1.011389</v>
+      </c>
+      <c r="H21" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_20</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>6.363285</v>
-      </c>
       <c r="D22" s="2" t="n">
-        <v>6.670769</v>
+        <v>76.49086</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.307484</v>
+        <v>76.79834700000001</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0.307484</v>
       </c>
       <c r="G22" s="2" t="n">
+        <v>0.307484</v>
+      </c>
+      <c r="H22" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_21</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>6.670769</v>
-      </c>
       <c r="D23" s="2" t="n">
-        <v>8.127791999999999</v>
+        <v>76.79834700000001</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1.457023</v>
+        <v>78.255371</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1.457023</v>
       </c>
       <c r="G23" s="2" t="n">
+        <v>1.457023</v>
+      </c>
+      <c r="H23" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_22</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>8.127791999999999</v>
-      </c>
       <c r="D24" s="2" t="n">
-        <v>9.314116</v>
+        <v>78.255371</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.186325</v>
+        <v>79.44169599999999</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1.186325</v>
       </c>
       <c r="G24" s="2" t="n">
+        <v>1.186325</v>
+      </c>
+      <c r="H24" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_23</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>9.314116</v>
-      </c>
       <c r="D25" s="2" t="n">
-        <v>10.616287</v>
+        <v>79.44169599999999</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.302171</v>
+        <v>80.743866</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>1.302171</v>
       </c>
       <c r="G25" s="2" t="n">
+        <v>1.302171</v>
+      </c>
+      <c r="H25" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_24</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>10.616287</v>
-      </c>
       <c r="D26" s="2" t="n">
-        <v>11.969785</v>
+        <v>80.743866</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1.353498</v>
+        <v>82.09736599999999</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1.353498</v>
       </c>
       <c r="G26" s="2" t="n">
+        <v>1.353498</v>
+      </c>
+      <c r="H26" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_25</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>11.969785</v>
-      </c>
       <c r="D27" s="2" t="n">
-        <v>13.020477</v>
+        <v>82.09736599999999</v>
       </c>
       <c r="E27" s="2" t="n">
+        <v>83.148056</v>
+      </c>
+      <c r="F27" s="2" t="n">
         <v>1.050693</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>0.981754</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>93.438728</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>71.27-85.13 (D)_002.jpg_Core_26</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>13.020477</v>
-      </c>
       <c r="D28" s="2" t="n">
-        <v>13.178054</v>
+        <v>83.148056</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.157577</v>
+        <v>83.305634</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0.157577</v>
       </c>
       <c r="G28" s="2" t="n">
+        <v>0.157577</v>
+      </c>
+      <c r="H28" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_27</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="D29" s="2" t="n">
+        <v>83.305634</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>84.529121</v>
+      </c>
+      <c r="F29" s="2" t="n">
         <v>1.223488</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>1.223488</v>
-      </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>1.162965</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>95.05323799999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_28</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>1.223488</v>
-      </c>
       <c r="D30" s="2" t="n">
-        <v>2.011967</v>
+        <v>84.529121</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.788479</v>
+        <v>85.31759599999999</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0.788479</v>
       </c>
       <c r="G30" s="2" t="n">
+        <v>0.788479</v>
+      </c>
+      <c r="H30" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_29</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>2.011967</v>
-      </c>
       <c r="D31" s="2" t="n">
-        <v>2.472908</v>
+        <v>85.31759599999999</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.460942</v>
+        <v>85.778542</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0.460942</v>
       </c>
       <c r="G31" s="2" t="n">
+        <v>0.460942</v>
+      </c>
+      <c r="H31" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_30</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>2.472908</v>
-      </c>
       <c r="D32" s="2" t="n">
-        <v>3.722834</v>
+        <v>85.778542</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1.249926</v>
+        <v>87.028465</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>1.249926</v>
       </c>
       <c r="G32" s="2" t="n">
+        <v>1.249926</v>
+      </c>
+      <c r="H32" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_31</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>3.722834</v>
-      </c>
       <c r="D33" s="2" t="n">
-        <v>4.321763</v>
+        <v>87.028465</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.598929</v>
+        <v>87.627396</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>0.598929</v>
       </c>
       <c r="G33" s="2" t="n">
+        <v>0.598929</v>
+      </c>
+      <c r="H33" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_32</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>4.321763</v>
-      </c>
       <c r="D34" s="2" t="n">
-        <v>4.940593</v>
+        <v>87.627396</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.618831</v>
+        <v>88.246223</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0.618831</v>
       </c>
       <c r="G34" s="2" t="n">
+        <v>0.618831</v>
+      </c>
+      <c r="H34" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_33</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>4.940593</v>
-      </c>
       <c r="D35" s="2" t="n">
-        <v>6.28964</v>
+        <v>88.246223</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1.349047</v>
+        <v>89.595276</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>1.349047</v>
       </c>
       <c r="G35" s="2" t="n">
+        <v>1.349047</v>
+      </c>
+      <c r="H35" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_34</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>6.28964</v>
-      </c>
       <c r="D36" s="2" t="n">
-        <v>6.825298</v>
+        <v>89.595276</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.535658</v>
+        <v>90.13093600000001</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0.535658</v>
       </c>
       <c r="G36" s="2" t="n">
+        <v>0.535658</v>
+      </c>
+      <c r="H36" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_35</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>6.825298</v>
-      </c>
       <c r="D37" s="2" t="n">
-        <v>7.680226</v>
+        <v>90.13093600000001</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.854927</v>
+        <v>90.98586299999999</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>0.854927</v>
       </c>
       <c r="G37" s="2" t="n">
+        <v>0.854927</v>
+      </c>
+      <c r="H37" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_36</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>7.680226</v>
-      </c>
       <c r="D38" s="2" t="n">
-        <v>9.085255999999999</v>
+        <v>90.98586299999999</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1.40503</v>
+        <v>92.39089199999999</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>1.40503</v>
       </c>
       <c r="G38" s="2" t="n">
+        <v>1.40503</v>
+      </c>
+      <c r="H38" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_37</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>9.085255999999999</v>
-      </c>
       <c r="D39" s="2" t="n">
-        <v>9.283530000000001</v>
+        <v>92.39089199999999</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.198275</v>
+        <v>92.58916499999999</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0.198275</v>
       </c>
       <c r="G39" s="2" t="n">
+        <v>0.198275</v>
+      </c>
+      <c r="H39" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_38</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>9.283530000000001</v>
-      </c>
       <c r="D40" s="2" t="n">
-        <v>10.15845</v>
+        <v>92.58916499999999</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.87492</v>
+        <v>93.46408099999999</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0.87492</v>
       </c>
       <c r="G40" s="2" t="n">
+        <v>0.87492</v>
+      </c>
+      <c r="H40" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_39</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>10.15845</v>
-      </c>
       <c r="D41" s="2" t="n">
-        <v>11.425339</v>
+        <v>93.46408099999999</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1.266889</v>
+        <v>94.73097199999999</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1.266889</v>
       </c>
       <c r="G41" s="2" t="n">
+        <v>1.266889</v>
+      </c>
+      <c r="H41" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>85.13-98.95 (D)_003.jpg_Core_40</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>11.425339</v>
-      </c>
       <c r="D42" s="2" t="n">
-        <v>12.72316</v>
+        <v>94.73097199999999</v>
       </c>
       <c r="E42" s="2" t="n">
+        <v>96.02879299999999</v>
+      </c>
+      <c r="F42" s="2" t="n">
         <v>1.29782</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>1.169199</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="H42" s="2" t="n">
         <v>90.089455</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_41</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="D43" s="2" t="n">
+        <v>96.02879299999999</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>96.31057</v>
+      </c>
+      <c r="F43" s="2" t="n">
         <v>0.28178</v>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>0.28178</v>
-      </c>
-      <c r="F43" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>0.141938</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="H43" s="2" t="n">
         <v>50.371872</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_42</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>0.28178</v>
-      </c>
       <c r="D44" s="2" t="n">
-        <v>1.105575</v>
+        <v>96.31057</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.823796</v>
+        <v>97.13436900000001</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0.823796</v>
       </c>
       <c r="G44" s="2" t="n">
+        <v>0.823796</v>
+      </c>
+      <c r="H44" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_43</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>1.105575</v>
-      </c>
       <c r="D45" s="2" t="n">
-        <v>2.18345</v>
+        <v>97.13436900000001</v>
       </c>
       <c r="E45" s="2" t="n">
+        <v>98.212242</v>
+      </c>
+      <c r="F45" s="2" t="n">
         <v>1.077875</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>0.86015</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>79.800552</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_44</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>2.18345</v>
-      </c>
       <c r="D46" s="2" t="n">
-        <v>2.793044</v>
+        <v>98.212242</v>
       </c>
       <c r="E46" s="2" t="n">
+        <v>98.821838</v>
+      </c>
+      <c r="F46" s="2" t="n">
         <v>0.6095930000000001</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>0.465851</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="H46" s="2" t="n">
         <v>76.420036</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_45</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>2.793044</v>
-      </c>
       <c r="D47" s="2" t="n">
-        <v>3.236013</v>
+        <v>98.821838</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.442969</v>
+        <v>99.264809</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>0.442969</v>
       </c>
       <c r="G47" s="2" t="n">
+        <v>0.442969</v>
+      </c>
+      <c r="H47" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_46</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>3.236013</v>
-      </c>
       <c r="D48" s="2" t="n">
-        <v>4.428214</v>
+        <v>99.264809</v>
       </c>
       <c r="E48" s="2" t="n">
+        <v>100.457008</v>
+      </c>
+      <c r="F48" s="2" t="n">
         <v>1.192201</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>1.153446</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="H48" s="2" t="n">
         <v>96.749245</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_47</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>4.428214</v>
-      </c>
       <c r="D49" s="2" t="n">
-        <v>5.403612</v>
+        <v>100.457008</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.975398</v>
+        <v>101.432404</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>0.975398</v>
       </c>
       <c r="G49" s="2" t="n">
+        <v>0.975398</v>
+      </c>
+      <c r="H49" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_48</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>5.403612</v>
-      </c>
       <c r="D50" s="2" t="n">
-        <v>5.612032</v>
+        <v>101.432404</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.20842</v>
+        <v>101.640823</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>0.20842</v>
       </c>
       <c r="G50" s="2" t="n">
+        <v>0.20842</v>
+      </c>
+      <c r="H50" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_49</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>5.612032</v>
-      </c>
       <c r="D51" s="2" t="n">
-        <v>6.836333</v>
+        <v>101.640823</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1.224301</v>
+        <v>102.865128</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>1.224301</v>
       </c>
       <c r="G51" s="2" t="n">
+        <v>1.224301</v>
+      </c>
+      <c r="H51" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_50</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>6.836333</v>
-      </c>
       <c r="D52" s="2" t="n">
-        <v>7.991852</v>
+        <v>102.865128</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1.15552</v>
+        <v>104.020645</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>1.15552</v>
       </c>
       <c r="G52" s="2" t="n">
+        <v>1.15552</v>
+      </c>
+      <c r="H52" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_51</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>7.991852</v>
-      </c>
       <c r="D53" s="2" t="n">
-        <v>9.15014</v>
+        <v>104.020645</v>
       </c>
       <c r="E53" s="2" t="n">
+        <v>105.178932</v>
+      </c>
+      <c r="F53" s="2" t="n">
         <v>1.158287</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>0.952829</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="H53" s="2" t="n">
         <v>82.26190200000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_52</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>9.15014</v>
-      </c>
       <c r="D54" s="2" t="n">
-        <v>10.407062</v>
+        <v>105.178932</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1.256922</v>
+        <v>106.435852</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>1.256922</v>
       </c>
       <c r="G54" s="2" t="n">
+        <v>1.256922</v>
+      </c>
+      <c r="H54" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>98.95-111.80 (D)_004.jpg_Core_53</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>10.407062</v>
-      </c>
       <c r="D55" s="2" t="n">
-        <v>11.543591</v>
+        <v>106.435852</v>
       </c>
       <c r="E55" s="2" t="n">
+        <v>107.572388</v>
+      </c>
+      <c r="F55" s="2" t="n">
         <v>1.136528</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>0.504447</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="H55" s="2" t="n">
         <v>44.384937</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_54</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="D56" s="2" t="n">
+        <v>107.572388</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>108.66436</v>
+      </c>
+      <c r="F56" s="2" t="n">
         <v>1.09197</v>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>1.09197</v>
-      </c>
-      <c r="F56" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>0.66827</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="H56" s="2" t="n">
         <v>61.198582</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_55</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>1.09197</v>
-      </c>
       <c r="D57" s="2" t="n">
-        <v>2.281821</v>
+        <v>108.66436</v>
       </c>
       <c r="E57" s="2" t="n">
+        <v>109.85421</v>
+      </c>
+      <c r="F57" s="2" t="n">
         <v>1.189851</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>1.05478</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="H57" s="2" t="n">
         <v>88.648079</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_56</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>2.281821</v>
-      </c>
       <c r="D58" s="2" t="n">
-        <v>3.483593</v>
+        <v>109.85421</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1.201771</v>
+        <v>111.055977</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>1.201771</v>
       </c>
       <c r="G58" s="2" t="n">
+        <v>1.201771</v>
+      </c>
+      <c r="H58" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_57</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>3.483593</v>
-      </c>
       <c r="D59" s="2" t="n">
-        <v>4.696352</v>
+        <v>111.055977</v>
       </c>
       <c r="E59" s="2" t="n">
+        <v>112.268738</v>
+      </c>
+      <c r="F59" s="2" t="n">
         <v>1.21276</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>1.110887</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="H59" s="2" t="n">
         <v>91.599915</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_58</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>4.696352</v>
-      </c>
       <c r="D60" s="2" t="n">
-        <v>5.827859</v>
+        <v>112.268738</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1.131507</v>
+        <v>113.400246</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>1.131507</v>
       </c>
       <c r="G60" s="2" t="n">
+        <v>1.131507</v>
+      </c>
+      <c r="H60" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_59</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>5.827859</v>
-      </c>
       <c r="D61" s="2" t="n">
-        <v>6.044003</v>
+        <v>113.400246</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.216143</v>
+        <v>113.616394</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>0.216143</v>
       </c>
       <c r="G61" s="2" t="n">
+        <v>0.216143</v>
+      </c>
+      <c r="H61" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_60</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>6.044003</v>
-      </c>
       <c r="D62" s="2" t="n">
-        <v>7.321891</v>
+        <v>113.616394</v>
       </c>
       <c r="E62" s="2" t="n">
+        <v>114.894279</v>
+      </c>
+      <c r="F62" s="2" t="n">
         <v>1.277889</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>1.180504</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="H62" s="2" t="n">
         <v>92.37919599999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_61</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>7.321891</v>
-      </c>
       <c r="D63" s="2" t="n">
-        <v>7.652739</v>
+        <v>114.894279</v>
       </c>
       <c r="E63" s="2" t="n">
+        <v>115.225128</v>
+      </c>
+      <c r="F63" s="2" t="n">
         <v>0.330847</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>0.08698</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="H63" s="2" t="n">
         <v>26.290026</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_62</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>7.652739</v>
-      </c>
       <c r="D64" s="2" t="n">
-        <v>8.311771999999999</v>
+        <v>115.225128</v>
       </c>
       <c r="E64" s="2" t="n">
+        <v>115.884163</v>
+      </c>
+      <c r="F64" s="2" t="n">
         <v>0.659034</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>0.55782</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="H64" s="2" t="n">
         <v>84.64207500000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_63</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>8.311771999999999</v>
-      </c>
       <c r="D65" s="2" t="n">
-        <v>9.510300000000001</v>
+        <v>115.884163</v>
       </c>
       <c r="E65" s="2" t="n">
+        <v>117.082687</v>
+      </c>
+      <c r="F65" s="2" t="n">
         <v>1.198527</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>1.02304</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="H65" s="2" t="n">
         <v>85.35805499999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_64</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>9.510300000000001</v>
-      </c>
       <c r="D66" s="2" t="n">
-        <v>10.470715</v>
+        <v>117.082687</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.960415</v>
+        <v>118.043106</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>0.960415</v>
       </c>
       <c r="G66" s="2" t="n">
+        <v>0.960415</v>
+      </c>
+      <c r="H66" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>111.80-124.58 (D)_005.jpg</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>111.80-124.58 (D)_005.jpg_Core_65</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>10.470715</v>
-      </c>
       <c r="D67" s="2" t="n">
-        <v>11.760663</v>
+        <v>118.043106</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1.289949</v>
+        <v>119.333054</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>1.289949</v>
       </c>
       <c r="G67" s="2" t="n">
+        <v>1.289949</v>
+      </c>
+      <c r="H67" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_66</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="D68" s="2" t="n">
-        <v>0.5605830000000001</v>
+        <v>119.333054</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.5605830000000001</v>
+        <v>119.893639</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>0.5605830000000001</v>
       </c>
       <c r="G68" s="2" t="n">
+        <v>0.5605830000000001</v>
+      </c>
+      <c r="H68" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_67</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>0.5605830000000001</v>
-      </c>
       <c r="D69" s="2" t="n">
-        <v>1.332276</v>
+        <v>119.893639</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.771693</v>
+        <v>120.665329</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>0.771693</v>
       </c>
       <c r="G69" s="2" t="n">
+        <v>0.771693</v>
+      </c>
+      <c r="H69" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_68</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>1.332276</v>
-      </c>
       <c r="D70" s="2" t="n">
-        <v>1.589918</v>
+        <v>120.665329</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.257642</v>
+        <v>120.922974</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>0.257642</v>
       </c>
       <c r="G70" s="2" t="n">
+        <v>0.257642</v>
+      </c>
+      <c r="H70" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_69</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>1.589918</v>
-      </c>
       <c r="D71" s="2" t="n">
-        <v>2.622659</v>
+        <v>120.922974</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1.03274</v>
+        <v>121.955711</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>1.03274</v>
       </c>
       <c r="G71" s="2" t="n">
+        <v>1.03274</v>
+      </c>
+      <c r="H71" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_70</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>2.622659</v>
-      </c>
       <c r="D72" s="2" t="n">
-        <v>3.921609</v>
+        <v>121.955711</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1.29895</v>
+        <v>123.254662</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>1.29895</v>
       </c>
       <c r="G72" s="2" t="n">
+        <v>1.29895</v>
+      </c>
+      <c r="H72" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_71</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>3.921609</v>
-      </c>
       <c r="D73" s="2" t="n">
-        <v>4.892056</v>
+        <v>123.254662</v>
       </c>
       <c r="E73" s="2" t="n">
+        <v>124.225113</v>
+      </c>
+      <c r="F73" s="2" t="n">
         <v>0.9704469999999999</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>0.737561</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="H73" s="2" t="n">
         <v>76.002197</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_72</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>4.892056</v>
-      </c>
       <c r="D74" s="2" t="n">
-        <v>5.146293</v>
+        <v>124.225113</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.254237</v>
+        <v>124.479347</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>0.254237</v>
       </c>
       <c r="G74" s="2" t="n">
+        <v>0.254237</v>
+      </c>
+      <c r="H74" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_73</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>5.146293</v>
-      </c>
       <c r="D75" s="2" t="n">
-        <v>6.518506</v>
+        <v>124.479347</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1.372213</v>
+        <v>125.851562</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>1.372213</v>
       </c>
       <c r="G75" s="2" t="n">
+        <v>1.372213</v>
+      </c>
+      <c r="H75" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_74</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>6.518506</v>
-      </c>
       <c r="D76" s="2" t="n">
-        <v>7.146133</v>
+        <v>125.851562</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.627628</v>
+        <v>126.479187</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>0.627628</v>
       </c>
       <c r="G76" s="2" t="n">
+        <v>0.627628</v>
+      </c>
+      <c r="H76" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_75</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>7.146133</v>
-      </c>
       <c r="D77" s="2" t="n">
-        <v>7.763544</v>
+        <v>126.479187</v>
       </c>
       <c r="E77" s="2" t="n">
+        <v>127.096596</v>
+      </c>
+      <c r="F77" s="2" t="n">
         <v>0.61741</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>0.541001</v>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="H77" s="2" t="n">
         <v>87.624268</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_76</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>7.763544</v>
-      </c>
       <c r="D78" s="2" t="n">
-        <v>9.028631000000001</v>
+        <v>127.096596</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1.265088</v>
+        <v>128.361679</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>1.265088</v>
       </c>
       <c r="G78" s="2" t="n">
+        <v>1.265088</v>
+      </c>
+      <c r="H78" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_77</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>9.028631000000001</v>
-      </c>
       <c r="D79" s="2" t="n">
-        <v>10.117956</v>
+        <v>128.361679</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>1.089326</v>
+        <v>129.451004</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>1.089326</v>
       </c>
       <c r="G79" s="2" t="n">
+        <v>1.089326</v>
+      </c>
+      <c r="H79" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_78</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>10.117956</v>
-      </c>
       <c r="D80" s="2" t="n">
-        <v>11.5217</v>
+        <v>129.451004</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1.403744</v>
+        <v>130.854752</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>1.403744</v>
       </c>
       <c r="G80" s="2" t="n">
+        <v>1.403744</v>
+      </c>
+      <c r="H80" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>124.58-138.03 (D)_006.jpg</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>124.58-138.03 (D)_006.jpg_Core_79</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>11.5217</v>
-      </c>
       <c r="D81" s="2" t="n">
-        <v>12.966981</v>
+        <v>130.854752</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1.445281</v>
+        <v>132.300034</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>1.445281</v>
       </c>
       <c r="G81" s="2" t="n">
+        <v>1.445281</v>
+      </c>
+      <c r="H81" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>138.03-147.00 (D)_007.jpg</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>138.03-147.00 (D)_007.jpg_Core_80</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="D82" s="2" t="n">
-        <v>1.302505</v>
+        <v>132.300034</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1.302505</v>
+        <v>133.602539</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>1.302505</v>
       </c>
       <c r="G82" s="2" t="n">
+        <v>1.302505</v>
+      </c>
+      <c r="H82" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>138.03-147.00 (D)_007.jpg</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>138.03-147.00 (D)_007.jpg_Core_81</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>1.302505</v>
-      </c>
       <c r="D83" s="2" t="n">
-        <v>2.686037</v>
+        <v>133.602539</v>
       </c>
       <c r="E83" s="2" t="n">
+        <v>134.986069</v>
+      </c>
+      <c r="F83" s="2" t="n">
         <v>1.383532</v>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="G83" s="2" t="n">
         <v>1.318068</v>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="H83" s="2" t="n">
         <v>95.268349</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>138.03-147.00 (D)_007.jpg</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>138.03-147.00 (D)_007.jpg_Core_82</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>2.686037</v>
-      </c>
       <c r="D84" s="2" t="n">
-        <v>2.787929</v>
+        <v>134.986069</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0.101892</v>
+        <v>135.087967</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>0.101892</v>
       </c>
       <c r="G84" s="2" t="n">
+        <v>0.101892</v>
+      </c>
+      <c r="H84" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>138.03-147.00 (D)_007.jpg</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>138.03-147.00 (D)_007.jpg_Core_83</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>2.787929</v>
-      </c>
       <c r="D85" s="2" t="n">
-        <v>4.079819</v>
+        <v>135.087967</v>
       </c>
       <c r="E85" s="2" t="n">
+        <v>136.379852</v>
+      </c>
+      <c r="F85" s="2" t="n">
         <v>1.29189</v>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="G85" s="2" t="n">
         <v>1.25708</v>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="H85" s="2" t="n">
         <v>97.30549600000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>138.03-147.00 (D)_007.jpg</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>138.03-147.00 (D)_007.jpg_Core_84</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>4.079819</v>
-      </c>
       <c r="D86" s="2" t="n">
-        <v>5.477285</v>
+        <v>136.379852</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1.397466</v>
+        <v>137.777313</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>1.397466</v>
       </c>
       <c r="G86" s="2" t="n">
+        <v>1.397466</v>
+      </c>
+      <c r="H86" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>138.03-147.00 (D)_007.jpg</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>138.03-147.00 (D)_007.jpg_Core_85</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>5.477285</v>
-      </c>
       <c r="D87" s="2" t="n">
-        <v>6.374898</v>
+        <v>137.777313</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>0.897614</v>
+        <v>138.674927</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>0.897614</v>
       </c>
       <c r="G87" s="2" t="n">
+        <v>0.897614</v>
+      </c>
+      <c r="H87" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>138.03-147.00 (D)_007.jpg</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>138.03-147.00 (D)_007.jpg_Core_86</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>6.374898</v>
-      </c>
       <c r="D88" s="2" t="n">
-        <v>6.789557</v>
+        <v>138.674927</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0.414659</v>
+        <v>139.089584</v>
       </c>
       <c r="F88" s="2" t="n">
         <v>0.414659</v>
       </c>
       <c r="G88" s="2" t="n">
+        <v>0.414659</v>
+      </c>
+      <c r="H88" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>138.03-147.00 (D)_007.jpg</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>138.03-147.00 (D)_007.jpg_Core_87</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>6.789557</v>
-      </c>
       <c r="D89" s="2" t="n">
-        <v>8.154127000000001</v>
+        <v>139.089584</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>1.36457</v>
+        <v>140.454163</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>1.36457</v>
       </c>
       <c r="G89" s="2" t="n">
+        <v>1.36457</v>
+      </c>
+      <c r="H89" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>138.03-147.00 (D)_007.jpg</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>138.03-147.00 (D)_007.jpg_Core_88</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>8.154127000000001</v>
-      </c>
       <c r="D90" s="2" t="n">
-        <v>8.779642000000001</v>
+        <v>140.454163</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0.625515</v>
+        <v>141.079681</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>0.625515</v>
       </c>
       <c r="G90" s="2" t="n">
+        <v>0.625515</v>
+      </c>
+      <c r="H90" s="2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2890,35 +3341,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="3" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Hole ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>img_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>core_run_id</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>fracture_id</t>
@@ -2926,31 +3370,31 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>fracture_type</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>position_m</t>
+          <t>Depth (m)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>length_m</t>
+          <t>Length (m)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_0</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_0_joint_0</t>
@@ -2962,20 +3406,20 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.200524</v>
+        <v>57.750523</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_1</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_1_joint_0</t>
@@ -2987,32 +3431,32 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.365785</v>
+        <v>59.137493</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_3</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>57.55-71.27 (D)_001.jpg_Core_3_joint_0</t>
@@ -3024,23 +3468,23 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.430895</v>
+        <v>60.397457</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_4</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_4_joint_2</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_4_joint_0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3049,35 +3493,48 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.133232</v>
+        <v>61.977249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_5</t>
-        </is>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>57.55-71.27 (D)_001.jpg_Core_4_joint_1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>61.781494</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_6</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_6_joint_1</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_4_joint_2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3086,48 +3543,35 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.172815</v>
+        <v>61.302563</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_7</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_7_joint_1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.118271</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_8</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_8_joint_2</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_6_joint_0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3136,23 +3580,23 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.608881</v>
+        <v>62.631573</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_9</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_9_joint_3</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_6_joint_1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3161,35 +3605,48 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.094929</v>
+        <v>63.663109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_10</t>
-        </is>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>57.55-71.27 (D)_001.jpg_Core_7_joint_0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>64.48622899999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_11</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_11_joint_1</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_7_joint_1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3198,48 +3655,51 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.858613</v>
+        <v>63.928402</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_12</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>57.55-71.27 (D)_001.jpg_Core_12_joint_3</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_8_broken_core_0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>broken_core</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.796947</v>
+        <v>65.366455</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.22377</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_13</t>
+          <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_13_joint_0</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_8_joint_1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3248,23 +3708,23 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.404132</v>
+        <v>65.475548</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_14</t>
+          <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_14_joint_0</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_8_joint_2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3273,48 +3733,51 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.585575</v>
+        <v>65.705223</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_15</t>
+          <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_15_joint_1</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_9_broken_core_0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>broken_core</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.220557</v>
+        <v>66.94008599999999</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0.097937</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_16</t>
+          <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_16_joint_1</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_9_joint_1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3323,35 +3786,48 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.263499</v>
+        <v>66.596001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_17</t>
-        </is>
+          <t>57.55-71.27 (D)_001.jpg</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>57.55-71.27 (D)_001.jpg_Core_9_joint_2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>66.799843</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_18</t>
+          <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_18_joint_0</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_9_joint_3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3360,47 +3836,60 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.161059</v>
+        <v>66.375366</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_19</t>
+          <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_20</t>
-        </is>
+          <t>57.55-71.27 (D)_001.jpg</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>57.55-71.27 (D)_001.jpg_Core_11_joint_0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>68.543716</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_21</t>
+          <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_21_joint_1</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_11_joint_1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3409,23 +3898,23 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.134801</v>
+        <v>68.697716</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_22</t>
+          <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_22_joint_0</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_12_joint_0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3434,23 +3923,23 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.670446</v>
+        <v>69.46553</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_23</t>
+          <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_23_joint_0</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_12_joint_1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3459,23 +3948,23 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.436319</v>
+        <v>69.198967</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_24</t>
+          <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_24_joint_1</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_12_joint_2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3484,23 +3973,23 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1.250562</v>
+        <v>68.97744</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_25</t>
+          <t>57.55-71.27 (D)_001.jpg</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_25_joint_1</t>
+          <t>57.55-71.27 (D)_001.jpg_Core_12_joint_3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3509,35 +3998,48 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.068939</v>
+        <v>69.62367999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>71.27-85.13 (D)_002.jpg_Core_26</t>
-        </is>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>71.27-85.13 (D)_002.jpg_Core_13_joint_0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>70.53170799999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_27</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_27_joint_2</t>
+          <t>71.27-85.13 (D)_002.jpg_Core_14_joint_0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3546,23 +4048,23 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.680487</v>
+        <v>71.288506</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_28</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_28_joint_0</t>
+          <t>71.27-85.13 (D)_002.jpg_Core_15_joint_0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3571,23 +4073,23 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.590863</v>
+        <v>72.14334100000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_29</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_29_joint_0</t>
+          <t>71.27-85.13 (D)_002.jpg_Core_15_joint_1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3596,23 +4098,23 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.243142</v>
+        <v>71.77533</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_30</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_30_joint_2</t>
+          <t>71.27-85.13 (D)_002.jpg_Core_16_joint_0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3621,23 +4123,23 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1.100311</v>
+        <v>73.533699</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_31</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_31_joint_0</t>
+          <t>71.27-85.13 (D)_002.jpg_Core_16_joint_1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3646,108 +4148,134 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.303584</v>
+        <v>73.101974</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_32</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_33</t>
-        </is>
+          <t>71.27-85.13 (D)_002.jpg</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>71.27-85.13 (D)_002.jpg_Core_18_joint_0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>74.239288</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_34</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_35</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_35_joint_1</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0.263175</v>
+          <t>71.27-85.13 (D)_002.jpg</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_36</t>
-        </is>
+          <t>71.27-85.13 (D)_002.jpg</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>71.27-85.13 (D)_002.jpg_Core_21_joint_0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>77.564674</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_37</t>
-        </is>
+          <t>71.27-85.13 (D)_002.jpg</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>71.27-85.13 (D)_002.jpg_Core_21_joint_1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>76.933151</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_38</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_38_joint_1</t>
+          <t>71.27-85.13 (D)_002.jpg_Core_22_joint_0</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3756,23 +4284,23 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.466604</v>
+        <v>78.925819</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_39</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_39_joint_1</t>
+          <t>71.27-85.13 (D)_002.jpg_Core_23_joint_0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3781,79 +4309,73 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.791432</v>
+        <v>79.87801399999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_40</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>85.13-98.95 (D)_003.jpg_Core_40_broken_core_3</t>
+          <t>71.27-85.13 (D)_002.jpg_Core_24_joint_0</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>broken_core</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.670868</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>0.128621</v>
+        <v>80.994095</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_41</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_41_broken_core_0</t>
+          <t>71.27-85.13 (D)_002.jpg_Core_24_joint_1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>broken_core</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.177792</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>0.139842</v>
+        <v>81.99443100000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_42</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_42_joint_0</t>
+          <t>71.27-85.13 (D)_002.jpg_Core_25_joint_0</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3862,23 +4384,23 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.226455</v>
+        <v>82.367706</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_43</t>
+          <t>71.27-85.13 (D)_002.jpg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_43_joint_1</t>
+          <t>71.27-85.13 (D)_002.jpg_Core_25_joint_1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3887,63 +4409,60 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.419564</v>
+        <v>82.16630600000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_44</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_44_broken_core_2</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>broken_core</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>0.028882</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0.11486</v>
+          <t>71.27-85.13 (D)_002.jpg</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_45</t>
-        </is>
+          <t>85.13-98.95 (D)_003.jpg</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>85.13-98.95 (D)_003.jpg_Core_27_joint_0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>84.422302</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_46</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_46_joint_1</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_27_joint_1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3952,23 +4471,23 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1.153446</v>
+        <v>83.366158</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_47</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_47_joint_1</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_27_joint_2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3977,35 +4496,48 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.720647</v>
+        <v>83.98612199999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_48</t>
-        </is>
+          <t>85.13-98.95 (D)_003.jpg</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>85.13-98.95 (D)_003.jpg_Core_28_joint_0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>85.11998699999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_49</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_49_joint_2</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_29_joint_0</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4014,23 +4546,23 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.780452</v>
+        <v>85.560738</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_50</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_50_joint_0</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_30_joint_0</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4039,51 +4571,48 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.793334</v>
+        <v>86.285599</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_51</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_51_broken_core_2</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_30_joint_1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>broken_core</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.784714</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>0.205458</v>
+        <v>86.4543</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_52</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_52_joint_1</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_30_joint_2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4092,129 +4621,84 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.254705</v>
+        <v>86.87885300000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_53</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>98.95-111.80 (D)_004.jpg_Core_53_broken_core_2</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_31_joint_0</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>broken_core</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1.009097</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>0.167167</v>
+        <v>87.332047</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_54</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_54_broken_core_0</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>broken_core</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>0.277707</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>0.4237</v>
+          <t>85.13-98.95 (D)_003.jpg</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_55</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_55_joint_3</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>0.340808</v>
+          <t>85.13-98.95 (D)_003.jpg</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_56</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_56_joint_1</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>1.066579</v>
+          <t>85.13-98.95 (D)_003.jpg</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_57</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_57_joint_4</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_35_joint_0</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4223,23 +4707,23 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.516903</v>
+        <v>90.524422</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_58</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_58_joint_2</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_35_joint_1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4248,116 +4732,97 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.139459</v>
+        <v>90.39411200000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_59</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_60</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_60_joint_5</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>0.756866</v>
+          <t>85.13-98.95 (D)_003.jpg</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_61</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_61_broken_core_0</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_38_joint_0</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>broken_core</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.147825</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>0.243867</v>
+        <v>92.909058</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_62</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_62_broken_core_0</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_38_joint_1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>broken_core</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.311351</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>0.101214</v>
+        <v>93.05577099999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_63</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_63_joint_2</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_39_joint_0</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4366,23 +4831,23 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.714327</v>
+        <v>94.474518</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_64</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_64_joint_0</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_39_joint_1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4391,23 +4856,23 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.395785</v>
+        <v>94.255516</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_65</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>111.80-124.58 (D)_005.jpg_Core_65_joint_3</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_40_joint_0</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4416,23 +4881,23 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1.074034</v>
+        <v>95.057762</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_66</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_66_joint_0</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_40_joint_1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4441,23 +4906,23 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.351227</v>
+        <v>95.810608</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_67</t>
+          <t>85.13-98.95 (D)_003.jpg</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_67_joint_0</t>
+          <t>85.13-98.95 (D)_003.jpg_Core_40_joint_2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4466,60 +4931,79 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.456137</v>
+        <v>95.278915</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_68</t>
-        </is>
+          <t>85.13-98.95 (D)_003.jpg</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>85.13-98.95 (D)_003.jpg_Core_40_broken_core_3</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>broken_core</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>95.40184000000001</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0.128621</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_69</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_69_joint_1</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_41_broken_core_0</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>broken_core</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.740193</v>
+        <v>96.20658899999999</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>0.139842</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_70</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_70_joint_1</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_42_joint_0</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4528,60 +5012,76 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.478664</v>
+        <v>96.537025</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_71</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_71_joint_2</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_43_broken_core_0</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>broken_core</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0.294345</v>
+        <v>97.934319</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>0.217725</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_72</t>
-        </is>
+          <t>98.95-111.80 (D)_004.jpg</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg_Core_43_joint_1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>97.553932</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_73</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_73_joint_0</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_44_joint_0</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4590,23 +5090,23 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.873637</v>
+        <v>98.679588</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_74</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_74_joint_1</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_44_joint_1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4615,73 +5115,63 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.165668</v>
+        <v>98.232315</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_75</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_75_joint_1</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_44_broken_core_2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>broken_core</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.428751</v>
+        <v>98.24112700000001</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0.11486</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_76</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_76_joint_0</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>0.584655</v>
+          <t>98.95-111.80 (D)_004.jpg</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_77</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_77_joint_0</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_46_joint_0</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4690,23 +5180,23 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.281194</v>
+        <v>99.660049</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_78</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_78_joint_2</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_46_joint_1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4715,23 +5205,23 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1.224572</v>
+        <v>100.418251</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_79</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>124.58-138.03 (D)_006.jpg_Core_79_joint_1</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_47_joint_0</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4740,23 +5230,23 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.405774</v>
+        <v>100.96769</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_80</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_80_joint_0</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_47_joint_1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4765,60 +5255,60 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0.569236</v>
+        <v>101.177658</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_81</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_81_joint_3</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>1.11281</v>
+          <t>98.95-111.80 (D)_004.jpg</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_82</t>
-        </is>
+          <t>98.95-111.80 (D)_004.jpg</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg_Core_49_joint_0</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>101.899048</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_83</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_83_joint_4</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_49_joint_1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4827,23 +5317,23 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0.533469</v>
+        <v>102.597946</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_84</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_84_joint_0</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_49_joint_2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4852,23 +5342,23 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0.277538</v>
+        <v>102.421272</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_85</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_85_joint_1</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_50_joint_0</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4877,23 +5367,23 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>0.29844</v>
+        <v>103.658463</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_86</t>
+          <t>98.95-111.80 (D)_004.jpg</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_86_joint_0</t>
+          <t>98.95-111.80 (D)_004.jpg_Core_51_joint_0</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4902,44 +5392,1966 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0.156759</v>
+        <v>104.345016</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg</t>
+          <t>COG-25-10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_87</t>
-        </is>
+          <t>98.95-111.80 (D)_004.jpg</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg_Core_51_joint_1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>104.627937</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg_Core_51_broken_core_2</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>broken_core</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>104.805359</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0.205458</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg_Core_52_joint_0</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>105.315216</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg_Core_52_joint_1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>105.43364</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg_Core_53_joint_0</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>106.873001</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg_Core_53_broken_core_1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>broken_core</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>107.351456</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0.371423</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>98.95-111.80 (D)_004.jpg_Core_53_broken_core_2</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>broken_core</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>107.444946</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0.167167</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_54_broken_core_0</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>broken_core</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>107.850098</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0.4237</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_55_joint_0</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>109.277443</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_55_joint_1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>109.084839</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_55_joint_2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>109.33284</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_55_joint_3</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>109.005165</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_56_joint_0</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>110.518044</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_56_joint_1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>110.920792</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_57_joint_0</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>111.64019</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_57_joint_1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>111.674751</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_57_joint_2</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>112.122734</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_57_joint_3</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>111.471481</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_57_joint_4</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>111.572884</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_58_joint_0</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>113.159142</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_58_joint_1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>112.802849</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_58_joint_2</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>112.408195</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_60_joint_0</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>114.275871</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_60_joint_1</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>113.912125</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_60_joint_2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>114.046951</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_60_joint_3</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>114.665138</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_60_joint_4</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>114.291748</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_60_joint_5</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>114.37326</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_61_broken_core_0</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>broken_core</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>115.042107</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>0.243867</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_62_broken_core_0</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>broken_core</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>115.536476</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>0.101214</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_63_joint_0</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>116.161163</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_63_broken_core_1</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>broken_core</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>116.564514</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>0.141513</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_63_joint_2</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>116.598488</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_64_joint_0</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>117.47847</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_65_joint_0</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>118.355927</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_65_joint_1</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>118.549606</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_65_joint_2</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>118.804741</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>111.80-124.58 (D)_005.jpg_Core_65_joint_3</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>119.117142</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_66_joint_0</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>119.68428</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_67_joint_0</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>120.349777</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_69_joint_0</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>121.329025</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_69_joint_1</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>121.66317</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_70_joint_0</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>122.762444</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_70_joint_1</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>122.434372</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_71_joint_0</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>124.04071</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_71_broken_core_1</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>broken_core</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>123.317375</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>0.170175</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_71_joint_2</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>123.549004</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_73_joint_0</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>125.352982</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_74_joint_0</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>126.209244</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_74_joint_1</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>126.017227</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_75_joint_0</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>126.984344</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_75_joint_1</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>126.907936</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_76_joint_0</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>127.681252</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_77_joint_0</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>128.642868</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_78_joint_0</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>129.83432</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_78_joint_1</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>130.051636</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_78_joint_2</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>130.675583</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_79_joint_0</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>131.968857</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>124.58-138.03 (D)_006.jpg_Core_79_joint_1</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>131.260529</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
           <t>138.03-147.00 (D)_007.jpg</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>138.03-147.00 (D)_007.jpg_Core_88</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_80_joint_0</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>132.869263</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_81_joint_0</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>133.875443</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_81_joint_1</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>134.649887</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_81_joint_2</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>133.751999</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_81_joint_3</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>134.715347</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_83_joint_0</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>135.793427</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_83_joint_1</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>135.828232</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_83_joint_2</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>135.510056</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_83_joint_3</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>136.211288</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_83_joint_4</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>135.621429</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_84_joint_0</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>136.657394</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_85_joint_0</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>138.440002</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_85_joint_1</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>138.07576</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_86_joint_0</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>138.83168</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg_Core_88_joint_0</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>140.742188</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>COG-25-10</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>138.03-147.00 (D)_007.jpg</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
         <is>
           <t>138.03-147.00 (D)_007.jpg_Core_88_joint_1</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>0.176138</v>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>140.630295</v>
       </c>
     </row>
   </sheetData>
